--- a/booking_forms/028_holiday_package_payment_form--booking_forms.xlsx
+++ b/booking_forms/028_holiday_package_payment_form--booking_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -442,7 +442,7 @@
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -801,7 +801,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Package Price</t>
+          <t>Package Price Total</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -847,7 +847,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Tax Amount</t>
+          <t>Tax Amount Total</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -870,7 +870,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Shipping Price</t>
+          <t>Shipping Price Total</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -893,7 +893,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Shipping Details</t>
+          <t>Shipping Details Total</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -911,12 +911,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>customer_details</t>
+          <t>customer_details_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Customer Details</t>
+          <t>Customer Details 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -934,12 +934,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>payment_method</t>
+          <t>payment_method_2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Payment Method</t>
+          <t>Payment Method 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -957,12 +957,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>comments_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Comments</t>
+          <t>Comments 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -980,12 +980,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>package_price</t>
+          <t>package_price_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Package Price</t>
+          <t>Package Price 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>tax_rate</t>
+          <t>tax_rate_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Tax Rate</t>
+          <t>Tax Rate 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>tax_amount</t>
+          <t>tax_amount_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Tax Amount</t>
+          <t>Tax Amount 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>shipping_price</t>
+          <t>shipping_price_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Shipping Price</t>
+          <t>Shipping Price 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>shipping_details</t>
+          <t>shipping_details_2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Shipping Details</t>
+          <t>Shipping Details 2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1101,7 +1101,7 @@
   <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
     <col width="6" customWidth="1" min="2" max="2"/>
     <col width="7" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1194,7 +1194,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>payment_method_choices</t>
+          <t>payment_method_2_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1211,7 +1211,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>payment_method_choices</t>
+          <t>payment_method_2_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
